--- a/projects/ALBATROSS_II/compute rail exit velocity.xlsx
+++ b/projects/ALBATROSS_II/compute rail exit velocity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Codes\TU Space Team\Lamarr_Flight_Simulation_RocketPy\Lamarr_Flight_Simulation_RocketPy\projects\ALBATROSS_II\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC8EA11-FEDF-4373-BE78-F05D0AC38309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A964CAC0-D9D6-4605-B863-75E3F0E55CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F7506AD-6491-4D7A-B043-943787E8C52C}"/>
+    <workbookView xWindow="6390" yWindow="1815" windowWidth="21600" windowHeight="11295" xr2:uid="{1F7506AD-6491-4D7A-B043-943787E8C52C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -146,7 +146,7 @@
     <t>17.0:1</t>
   </si>
   <si>
-    <t>?</t>
+    <t>3 kg payload</t>
   </si>
 </sst>
 </file>
@@ -168,7 +168,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,12 +193,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -340,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -398,7 +392,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -767,6 +760,9 @@
       <c r="A1" s="25" t="s">
         <v>26</v>
       </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2" spans="1:12" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
@@ -812,24 +808,28 @@
     </row>
     <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17">
-        <v>2</v>
-      </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="18"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="21">
+        <v>1.88</v>
+      </c>
+      <c r="C4" s="18">
+        <v>4.1369999999999996</v>
+      </c>
       <c r="E4" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="33" t="s">
-        <v>28</v>
+      <c r="F4" s="19">
+        <v>1.6</v>
       </c>
       <c r="G4" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" s="19">
         <v>7</v>
       </c>
       <c r="I4" s="19">
-        <v>6.0449999999999999</v>
+        <v>5.9489999999999998</v>
       </c>
       <c r="J4" s="1">
         <f>RADIANS(2)</f>
@@ -841,20 +841,28 @@
     </row>
     <row r="5" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="18"/>
+        <v>2</v>
+      </c>
+      <c r="B5" s="17">
+        <v>2.032</v>
+      </c>
+      <c r="C5" s="18">
+        <v>2.76</v>
+      </c>
       <c r="L5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19">
-        <v>1.2</v>
-      </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="B6" s="19">
+        <v>2.2050000000000001</v>
+      </c>
+      <c r="C6" s="20">
+        <v>1.381</v>
+      </c>
       <c r="L6" t="s">
         <v>25</v>
       </c>
@@ -929,87 +937,87 @@
       </c>
       <c r="B12" s="22">
         <f>B4</f>
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="C12" s="2">
         <f>C4</f>
-        <v>0</v>
+        <v>4.1369999999999996</v>
       </c>
       <c r="D12" s="2">
         <f>RADIANS(C12)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="e">
+        <v>7.2204271155005412E-2</v>
+      </c>
+      <c r="E12" s="2">
         <f>A12/TAN($D$12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F12" s="2" t="e">
+        <v>13.825519748404485</v>
+      </c>
+      <c r="F12" s="2">
         <f t="shared" ref="F12:F23" si="0">E12^2/(2*$I$4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G12" s="3" t="e">
+        <v>16.065304783452884</v>
+      </c>
+      <c r="G12" s="3">
         <f t="shared" ref="G12:G23" si="1">F12/9.81+COS($J$4)</f>
-        <v>#DIV/0!</v>
+        <v>2.6370365745678095</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="B13" s="23"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="4" t="e">
+      <c r="E13" s="4">
         <f>A13/TAN($D$12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F13" s="4" t="e">
+        <v>27.65103949680897</v>
+      </c>
+      <c r="F13" s="4">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G13" s="5" t="e">
+        <v>64.261219133811537</v>
+      </c>
+      <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7.5499738172139512</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" s="23"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="4" t="e">
+      <c r="E14" s="4">
         <f>A14/TAN($D$12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F14" s="4" t="e">
+        <v>41.476559245213451</v>
+      </c>
+      <c r="F14" s="4">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G14" s="5" t="e">
+        <v>144.58774305107593</v>
+      </c>
+      <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>15.738202554957518</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="B15" s="24"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="6" t="e">
+      <c r="E15" s="6">
         <f>A15/TAN($D$12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F15" s="6" t="e">
+        <v>48.389319119415696</v>
+      </c>
+      <c r="F15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G15" s="7" t="e">
+        <v>196.79998359729782</v>
+      </c>
+      <c r="G15" s="7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>21.060551234490841</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1018,87 +1026,87 @@
       </c>
       <c r="B16" s="22">
         <f>B5</f>
-        <v>0</v>
+        <v>2.032</v>
       </c>
       <c r="C16" s="2">
         <f>C5</f>
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="D16" s="2">
         <f>RADIANS(C16)</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="e">
+        <v>4.8171087355043489E-2</v>
+      </c>
+      <c r="E16" s="2">
         <f>A16/TAN($D$16)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F16" s="2" t="e">
+        <v>20.743280889650482</v>
+      </c>
+      <c r="F16" s="2">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G16" s="3" t="e">
+        <v>36.164372337110343</v>
+      </c>
+      <c r="G16" s="3">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>4.6858711875808021</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="B17" s="23"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="4" t="e">
+      <c r="E17" s="4">
         <f>A17/TAN($D$16)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F17" s="4" t="e">
+        <v>41.486561779300963</v>
+      </c>
+      <c r="F17" s="4">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G17" s="5" t="e">
+        <v>144.65748934844137</v>
+      </c>
+      <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>15.745312269265922</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" s="23"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="4" t="e">
+      <c r="E18" s="4">
         <f>A18/TAN($D$16)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F18" s="4" t="e">
+        <v>62.229842668951441</v>
+      </c>
+      <c r="F18" s="4">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G18" s="5" t="e">
+        <v>325.47935103399305</v>
+      </c>
+      <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>34.177714072074451</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="B19" s="24"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
-      <c r="E19" s="6" t="e">
+      <c r="E19" s="6">
         <f>A19/TAN($D$16)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F19" s="6" t="e">
+        <v>72.601483113776681</v>
+      </c>
+      <c r="F19" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G19" s="7" t="e">
+        <v>443.01356112960173</v>
+      </c>
+      <c r="G19" s="7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>46.158775243900003</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1107,87 +1115,87 @@
       </c>
       <c r="B20" s="22">
         <f>B6</f>
-        <v>0</v>
+        <v>2.2050000000000001</v>
       </c>
       <c r="C20" s="4">
         <f>C6</f>
-        <v>0</v>
+        <v>1.381</v>
       </c>
       <c r="D20" s="2">
         <f>RADIANS(C20)</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="4" t="e">
+        <v>2.4102996970041691E-2</v>
+      </c>
+      <c r="E20" s="4">
         <f>A20/TAN($D$20)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F20" s="4" t="e">
+        <v>41.480581948147254</v>
+      </c>
+      <c r="F20" s="4">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G20" s="5" t="e">
+        <v>144.61579078475037</v>
+      </c>
+      <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>15.74106165115267</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="B21" s="23"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="4" t="e">
+      <c r="E21" s="4">
         <f>A21/TAN($D$20)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F21" s="4" t="e">
+        <v>82.961163896294508</v>
+      </c>
+      <c r="F21" s="4">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G21" s="5" t="e">
+        <v>578.46316313900149</v>
+      </c>
+      <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>59.966074123553398</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" s="23"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="4" t="e">
+      <c r="E22" s="4">
         <f>A22/TAN($D$20)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F22" s="4" t="e">
+        <v>124.44174584444175</v>
+      </c>
+      <c r="F22" s="4">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G22" s="5" t="e">
+        <v>1301.5421170627533</v>
+      </c>
+      <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>133.67442824422125</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="15">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="B23" s="24"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
-      <c r="E23" s="6" t="e">
+      <c r="E23" s="6">
         <f>A23/TAN($D$20)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F23" s="6" t="e">
+        <v>145.18203681851537</v>
+      </c>
+      <c r="F23" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G23" s="7" t="e">
+        <v>1771.5434371131917</v>
+      </c>
+      <c r="G23" s="7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>181.58485842265532</v>
       </c>
     </row>
   </sheetData>
